--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1515-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1515-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D275EB7-1743-473C-AF75-81D505AD2090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D08DEA91-60BD-4A3A-8D5C-00519F64BBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{67F58A6F-9641-4BF0-A886-368570D02FB3}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{60AD2228-EAC5-4C55-A3FB-651E103F56BF}"/>
   </bookViews>
   <sheets>
     <sheet name="1515-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1472,24 +1472,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4D4744-5BAB-4B61-86F2-1CBFAC1956AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC88C22-39F7-4212-9D36-7AC5073DC771}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1522,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1559,7 +1558,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1611,7 +1610,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1679,7 +1678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1751,7 +1750,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1823,7 +1822,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1895,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1967,7 +1966,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2039,7 +2038,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2111,7 +2110,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2183,7 +2182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2255,7 +2254,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2327,7 +2326,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2399,7 +2398,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2543,7 +2542,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2687,7 +2686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2759,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2831,7 +2830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2903,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2975,7 +2974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3047,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3119,7 +3118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3191,7 +3190,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3263,7 +3262,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3335,7 +3334,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3407,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3479,7 +3478,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3551,7 +3550,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3623,7 +3622,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3695,7 +3694,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3767,7 +3766,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3839,7 +3838,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3911,7 +3910,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4055,7 +4054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36" t="s">
         <v>49</v>
       </c>
